--- a/Magnetostricción/toma de datos magnto.xlsx
+++ b/Magnetostricción/toma de datos magnto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/av_bustos_uniandes_edu_co/Documents/Documentos/Descargas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/av_bustos_uniandes_edu_co/Documents/Escritorio/Lab-Intermedio/Magnetostricción/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04AD9261-CA03-46C6-B2DD-EA354FB9D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{04AD9261-CA03-46C6-B2DD-EA354FB9D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED6647A7-F4B6-4A98-8F08-7E1B989BDD8C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{C55408EC-441E-467B-A07B-90319C2E4185}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{C55408EC-441E-467B-A07B-90319C2E4185}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2140,7 +2140,7 @@
                   <c:v>-8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-7</c:v>
+                  <c:v>-8</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-7.5</c:v>
@@ -2149,7 +2149,7 @@
                   <c:v>-7</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-6.5</c:v>
+                  <c:v>-7</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>-6</c:v>
@@ -5912,16 +5912,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>761999</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>42862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6829,10 +6829,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>1.23</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>-6.5</v>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
         <v>2.13</v>
       </c>
       <c r="B20">
-        <v>-7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6897,7 +6897,7 @@
         <v>1.21</v>
       </c>
       <c r="B23">
-        <v>-6.5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">

--- a/Magnetostricción/toma de datos magnto.xlsx
+++ b/Magnetostricción/toma de datos magnto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/av_bustos_uniandes_edu_co/Documents/Escritorio/Lab-Intermedio/Magnetostricción/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{04AD9261-CA03-46C6-B2DD-EA354FB9D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED6647A7-F4B6-4A98-8F08-7E1B989BDD8C}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{04AD9261-CA03-46C6-B2DD-EA354FB9D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AA7E54C-366F-480E-B6CB-6FA8EBB6259D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{C55408EC-441E-467B-A07B-90319C2E4185}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{C55408EC-441E-467B-A07B-90319C2E4185}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -64,10 +64,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -99,11 +106,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5949,6 +5957,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -6554,7 +6566,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="4">
         <v>3.13</v>
       </c>
       <c r="B33" s="1">

--- a/Magnetostricción/toma de datos magnto.xlsx
+++ b/Magnetostricción/toma de datos magnto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/av_bustos_uniandes_edu_co/Documents/Escritorio/Lab-Intermedio/Magnetostricción/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{04AD9261-CA03-46C6-B2DD-EA354FB9D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AA7E54C-366F-480E-B6CB-6FA8EBB6259D}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{04AD9261-CA03-46C6-B2DD-EA354FB9D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96119727-2579-48BE-AA95-E66929945D7C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{C55408EC-441E-467B-A07B-90319C2E4185}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{C55408EC-441E-467B-A07B-90319C2E4185}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -90,6 +90,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -106,12 +112,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6865,10 +6872,10 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="5">
         <v>2.98</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="5">
         <v>-8</v>
       </c>
     </row>
